--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136985802</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136986011</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136986195</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136986183</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136985778</v>
       </c>
       <c r="B8" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136985802</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136986011</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136986195</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136986183</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>136985778</v>
       </c>
       <c r="B8" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -933,11 +933,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lars-Jons mosse, Dlr</t>
@@ -1050,11 +1046,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lars-Jons mosse, Dlr</t>
@@ -1167,16 +1159,8 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lars-Jons mosse, Dlr</t>
@@ -1289,11 +1273,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lars-Jons mosse, Dlr</t>
@@ -1411,16 +1391,8 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lars-Jons mosse, Dlr</t>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136985802</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136986011</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136986195</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136986183</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136985778</v>
       </c>
       <c r="B8" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136985802</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136986011</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136986195</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136986183</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136985778</v>
       </c>
       <c r="B8" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136985802</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136986011</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136986195</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136986183</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35101-2026 artfynd.xlsx
+++ b/artfynd/A 35101-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136985665</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986277</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136985802</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136986011</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>136986195</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136986183</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>136985778</v>
       </c>
       <c r="B8" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
